--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_6.xlsx
@@ -513,496 +513,496 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_13</t>
+          <t>model_23_6_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9781378574171787</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7400084294975758</v>
+        <v>0.7128654963365189</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8820192942975732</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9825349328046205</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9338586443685432</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1461922481172364</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.738564829100814</v>
+        <v>0.1704554449393573</v>
       </c>
       <c r="I2" t="n">
-        <v>0.77740062377805</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03684871588407956</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4071246698310647</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2346283154842424</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3823509488902001</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N2" t="n">
-        <v>1.014991183485363</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O2" t="n">
-        <v>0.398628420360033</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P2" t="n">
-        <v>121.8456655110522</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q2" t="n">
-        <v>193.7593391782761</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_14</t>
+          <t>model_23_6_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9774557382933006</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7399863135949886</v>
+        <v>0.7128654963365189</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8748499306496966</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9824237199812549</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9300022480033446</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1507535818394792</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.73871271824325</v>
+        <v>0.1704554449393573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8246411258480105</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0370833585387582</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4308622252822636</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2312128603245487</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3882699857566628</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N3" t="n">
-        <v>1.015458922313165</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4047994428799966</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P3" t="n">
-        <v>121.7842173670558</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q3" t="n">
-        <v>193.6978910342796</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_12</t>
+          <t>model_23_6_7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9787992241593917</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7399490296106292</v>
+        <v>0.7128654956957796</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8897026605839538</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E4" t="n">
-        <v>0.98275387081917</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9380086189014151</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1417696856667442</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.738962036418338</v>
+        <v>0.1704554453197278</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7267732461218011</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03638678896423948</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3815800314520589</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2379167857716626</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3765231542239391</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N4" t="n">
-        <v>1.014537674862131</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3925525244096313</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P4" t="n">
-        <v>121.9071029401216</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q4" t="n">
-        <v>193.8207766073454</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_15</t>
+          <t>model_23_6_8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9767708036043805</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7399048861923092</v>
+        <v>0.7128654956957796</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8681873937251436</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9823915912225355</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9264306785670513</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1553337432581219</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.739257223659905</v>
+        <v>0.1704554453197278</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8685420360032318</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03715114548103075</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4528465649385575</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2277645131382539</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3941240201486353</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N5" t="n">
-        <v>1.015928591814139</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4109026956355571</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P5" t="n">
-        <v>121.7243585890546</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q5" t="n">
-        <v>193.6380322562784</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_16</t>
+          <t>model_23_6_9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9760962699232751</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7397815102988106</v>
+        <v>0.7128654956957796</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8620175633967071</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9824153230997026</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9231323903141617</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1598443530896157</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.740082238827825</v>
+        <v>0.1704554453197278</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9091963948441506</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03710107472038929</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4731487571622482</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2243516436834632</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3998053940226616</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N6" t="n">
-        <v>1.016391129195468</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4168259373574659</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P6" t="n">
-        <v>121.6671094608172</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q6" t="n">
-        <v>193.580783128041</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_11</t>
+          <t>model_23_6_10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9794157937409749</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7397798987080733</v>
+        <v>0.7128654956957796</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8978980479931884</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9831161979595611</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9424572216402909</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1376466820356558</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.740093015542506</v>
+        <v>0.1704554453197278</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6727720495184253</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03562233213713419</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K7" t="n">
-        <v>0.354197225279078</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2409600494223739</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3710076576509652</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N7" t="n">
-        <v>1.014114884291903</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O7" t="n">
-        <v>0.386802221728894</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P7" t="n">
-        <v>121.9661303040763</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q7" t="n">
-        <v>193.8798039713001</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_17</t>
+          <t>model_23_6_22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9754417177505212</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7396296051215697</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8563216373994349</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9824769420263144</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92009425118528</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1642213464827564</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.741098029447493</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9467280945988663</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03697106787332717</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4918496346682812</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2210282575282513</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4052423305662384</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N8" t="n">
-        <v>1.016839964971071</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4224943355457129</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P8" t="n">
-        <v>121.6130801749468</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q8" t="n">
-        <v>193.5267538421706</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_10</t>
+          <t>model_23_6_21</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9799556990466303</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7394649147224077</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9065904511073499</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E9" t="n">
-        <v>0.983663106525996</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9472034978213661</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1340363327707025</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.742199314905019</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6154959079421639</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03446843572473093</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3249821282388183</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2436128266205623</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3661097277739318</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N9" t="n">
-        <v>1.013744663510882</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3816957768368827</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P9" t="n">
-        <v>122.0192887514064</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q9" t="n">
-        <v>193.9329624186302</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_18</t>
+          <t>model_23_6_20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9748137280764672</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7394596260748199</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8510773782584713</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9825627042489118</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9173020209672789</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1684207163247829</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.742234680115791</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9812836628434034</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.03679012223259616</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5090368512704063</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2178335048078118</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4103909310947098</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N10" t="n">
-        <v>1.017270586461851</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4278621226577538</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P10" t="n">
-        <v>121.5625803323687</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q10" t="n">
-        <v>193.4762539995925</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="11">
@@ -1012,492 +1012,492 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9742167717095346</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7392794737862324</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8462604987459519</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9826627691579397</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9147409772455148</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1724125662991922</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7434393592991</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I11" t="n">
-        <v>1.013023133423797</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03657900003297982</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5248010289122417</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2147885264743712</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M11" t="n">
-        <v>0.415225921998124</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N11" t="n">
-        <v>1.017679927970605</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4329029491337373</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P11" t="n">
-        <v>121.5157300660847</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q11" t="n">
-        <v>193.4294037333086</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_20</t>
+          <t>model_23_6_18</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9736536058911885</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7390952501183129</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8418460448809215</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9827697118577969</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9123965064925458</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1761784587196125</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.74467126381475</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I12" t="n">
-        <v>1.042110933567744</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03635336670910917</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5392321192961397</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2119129547688435</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4197361775206094</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N12" t="n">
-        <v>1.018066098817471</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4376052155713309</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P12" t="n">
-        <v>121.4725156553331</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q12" t="n">
-        <v>193.3861893225569</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_9</t>
+          <t>model_23_6_17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9803771839489521</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7389583135610628</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D13" t="n">
-        <v>0.915749400121622</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9844389662245635</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9522387055554289</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1312178612881173</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.745586959203616</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5551455935881787</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03283148619120805</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2939885499141836</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2457014618032818</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3622400603027187</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N13" t="n">
-        <v>1.013455645292147</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3776613696101041</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P13" t="n">
-        <v>122.0617925477426</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q13" t="n">
-        <v>193.9754662149665</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_21</t>
+          <t>model_23_6_16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.97312547476276</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7389113865755834</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8378072528502387</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9828784685348285</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9102534124546587</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1797100740072344</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.745900760171596</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I14" t="n">
-        <v>1.068723415882283</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03612390616094163</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5524236610216124</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2092140845664013</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4239222499553832</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N14" t="n">
-        <v>1.018428245876964</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4419694977760175</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P14" t="n">
-        <v>121.432820853247</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q14" t="n">
-        <v>193.3464945204709</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_22</t>
+          <t>model_23_6_15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9726328692474373</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7387311425472001</v>
+        <v>0.7128654955887277</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8341187814186823</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9829856039002121</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9082975515957047</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1830041293564367</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.747106052819343</v>
+        <v>0.1704554453832784</v>
       </c>
       <c r="I15" t="n">
-        <v>1.093027559298001</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03589786634122678</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5644627128196141</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2066996601308172</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4277898191360293</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N15" t="n">
-        <v>1.018766032516043</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4460017173836557</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P15" t="n">
-        <v>121.3964931232121</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q15" t="n">
-        <v>193.3101667904359</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_23</t>
+          <t>model_23_6_12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9721753568155834</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7385569768959184</v>
+        <v>0.7128654955133256</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8307551352986784</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9830886097824213</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9065148445606055</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1860635170948945</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.748270699331423</v>
+        <v>0.1704554454280404</v>
       </c>
       <c r="I16" t="n">
-        <v>1.115191357830069</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03568053912195776</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5754359383627128</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2043630213567716</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4313508051399632</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N16" t="n">
-        <v>1.019079755326457</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4497143019340343</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P16" t="n">
-        <v>121.3633343476116</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q16" t="n">
-        <v>193.2770080148354</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_24</t>
+          <t>model_23_6_13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9717520951447742</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7383904940629966</v>
+        <v>0.7128654955133256</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8276920123408154</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9831864644179167</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9048921096320753</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1888938698365366</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.749383970801754</v>
+        <v>0.1704554454280404</v>
       </c>
       <c r="I17" t="n">
-        <v>1.135374943645852</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03547408027350495</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5854244760286538</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L17" t="n">
-        <v>0.202200693467025</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4346192239610859</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N17" t="n">
-        <v>1.019369991900726</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4531218641109319</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P17" t="n">
-        <v>121.3331399137978</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q17" t="n">
-        <v>193.2468135810216</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_8</t>
+          <t>model_23_6_11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9806256831673584</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7382017564507867</v>
+        <v>0.7128654955133256</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9253228642340008</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9854870683613386</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9575424555314282</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1295561458704001</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.750646060083658</v>
+        <v>0.1704554454280404</v>
       </c>
       <c r="I18" t="n">
-        <v>0.492063948768631</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03062014526572122</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2613419941060909</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2470392297694011</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3599390863332296</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N18" t="n">
-        <v>1.013285245828097</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3752624384150611</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P18" t="n">
-        <v>122.0872818659145</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q18" t="n">
-        <v>194.0009555331383</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_7</t>
+          <t>model_23_6_14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9806297761563182</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7371212143908439</v>
+        <v>0.7128654955133256</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9352303380500468</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9868401226529734</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9630772245965039</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1295287760343803</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.757871649813934</v>
+        <v>0.1704554454280404</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4267814411009352</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.02776540027044419</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2272734297911124</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2474359423109131</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3599010642306859</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N19" t="n">
-        <v>1.013282439207096</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3752227976328955</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P19" t="n">
-        <v>122.0877044275351</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q19" t="n">
-        <v>194.001378094759</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9802968378446706</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7356224507389652</v>
+        <v>0.7128654951043616</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9453565922081538</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9885085276282802</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9687831476159159</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1317551360574076</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.767893889255219</v>
+        <v>0.1704554456708191</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3600573420020303</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02424531184324765</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1921513491627144</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2467364306956366</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3629809031580141</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N20" t="n">
-        <v>1.013510739763654</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3784337516795055</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P20" t="n">
-        <v>122.0536202179251</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q20" t="n">
-        <v>193.967293885149</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9795069210080601</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7335860011952247</v>
+        <v>0.7128654951043616</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9555403833174537</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E21" t="n">
-        <v>0.990462621118183</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9745688378698043</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1370373135810541</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7815116367312</v>
+        <v>0.1704554456708191</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2929541193720248</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02012246278605048</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K21" t="n">
-        <v>0.156538271506972</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L21" t="n">
-        <v>0.244883020664729</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3701855123867682</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N21" t="n">
-        <v>1.014052397023044</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3859450760387248</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P21" t="n">
-        <v>121.9750040566646</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q21" t="n">
-        <v>193.8886777238884</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9781053753070801</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7308603879691019</v>
+        <v>0.7128654951043616</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9655628644125753</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9926151044653866</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9803021773770758</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G22" t="n">
-        <v>0.146409456137032</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.799737824924577</v>
+        <v>0.1704554456708191</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2269138036376619</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0155810403901892</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K22" t="n">
-        <v>0.121247432188022</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2420231525832997</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3826348861996668</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N22" t="n">
-        <v>1.015013456932288</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O22" t="n">
-        <v>0.398924445468595</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P22" t="n">
-        <v>121.8426961768818</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q22" t="n">
-        <v>193.7563698441056</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9758952946883681</v>
+        <v>0.9999263694255129</v>
       </c>
       <c r="C23" t="n">
-        <v>0.727254947255205</v>
+        <v>0.7128654951043616</v>
       </c>
       <c r="D23" t="n">
-        <v>0.975133950452027</v>
+        <v>0.9997460653257515</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9948152212343656</v>
+        <v>0.9995013370301891</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9858020834482238</v>
+        <v>0.9996639445085993</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1611882754108447</v>
+        <v>4.371028969071967e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.823847423579934</v>
+        <v>0.1704554456708191</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1638478284597386</v>
+        <v>5.955371742230982e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01093911849976818</v>
+        <v>0.0002136355922241635</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08739346258094795</v>
+        <v>0.0001365944592225912</v>
       </c>
       <c r="L23" t="n">
-        <v>0.241256721789006</v>
+        <v>0.001741122342325455</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4014825966475318</v>
+        <v>0.006611375778967617</v>
       </c>
       <c r="N23" t="n">
-        <v>1.016528940785119</v>
+        <v>1.000050489536791</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4185745419703649</v>
+        <v>0.006892835733312844</v>
       </c>
       <c r="P23" t="n">
-        <v>121.6503643694763</v>
+        <v>138.0758540430987</v>
       </c>
       <c r="Q23" t="n">
-        <v>193.5640380367001</v>
+        <v>209.9895277103226</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9726290312538953</v>
+        <v>0.9999263754483461</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7225307185214747</v>
+        <v>0.7128652799263899</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9838768111964951</v>
+        <v>0.9997460777286551</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9968605384446961</v>
+        <v>0.9995013824061324</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9908321515153435</v>
+        <v>0.9996639710376358</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1830297940369245</v>
+        <v>4.37067142767776e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.855438362875462</v>
+        <v>0.1704555734097583</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1062392105430353</v>
+        <v>5.955080864659403e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006623800846926441</v>
+        <v>0.0002136161524078265</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05643152081996083</v>
+        <v>0.000136583676124303</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2409998603282472</v>
+        <v>0.001741202467651817</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4278198149185291</v>
+        <v>0.006611105374805155</v>
       </c>
       <c r="N24" t="n">
-        <v>1.018768664283043</v>
+        <v>1.000050485406848</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4460329901487163</v>
+        <v>0.006892553817485372</v>
       </c>
       <c r="P24" t="n">
-        <v>121.3962126608954</v>
+        <v>138.0760176457747</v>
       </c>
       <c r="Q24" t="n">
-        <v>193.3098863281193</v>
+        <v>209.9896913129986</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9680000098165846</v>
+        <v>0.9999263764055933</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7163915262135747</v>
+        <v>0.7128651837675973</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9913093795875911</v>
+        <v>0.9997460816622732</v>
       </c>
       <c r="E25" t="n">
-        <v>0.99853477908692</v>
+        <v>0.9995013885447002</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9950973079840331</v>
+        <v>0.9996639758887256</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2139840817029046</v>
+        <v>4.370614601345083e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.89649117010677</v>
+        <v>0.1704556304937714</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05726439496526873</v>
+        <v>5.954988611963723e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.003091400023229147</v>
+        <v>0.0002136135225423048</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03017789474116291</v>
+        <v>0.000136581704330971</v>
       </c>
       <c r="L25" t="n">
-        <v>0.241451944587999</v>
+        <v>0.001741170056908033</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4625841347289211</v>
+        <v>0.006611062396729502</v>
       </c>
       <c r="N25" t="n">
-        <v>1.021942850411485</v>
+        <v>1.00005048475045</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4822772990254995</v>
+        <v>0.006892509009744062</v>
       </c>
       <c r="P25" t="n">
-        <v>121.0837073025856</v>
+        <v>138.0760436494234</v>
       </c>
       <c r="Q25" t="n">
-        <v>192.9973809698095</v>
+        <v>209.9897173166472</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9616342248576437</v>
+        <v>0.9999263765273503</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7084723847047506</v>
+        <v>0.7128651703111351</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9968266311230941</v>
+        <v>0.9997460923727292</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9996442968686536</v>
+        <v>0.99950138373826</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9982405224249291</v>
+        <v>0.9996639748200138</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2565521150350875</v>
+        <v>4.370607373326924e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.949446505840571</v>
+        <v>0.1704556384821087</v>
       </c>
       <c r="I26" t="n">
-        <v>0.02091002024184156</v>
+        <v>5.954737426313043e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0007504811449868939</v>
+        <v>0.0002136155817019754</v>
       </c>
       <c r="K26" t="n">
-        <v>0.01083023956777224</v>
+        <v>0.0001365821387238394</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2444523219465922</v>
+        <v>0.001741192102065642</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5065097383418087</v>
+        <v>0.006611056930118606</v>
       </c>
       <c r="N26" t="n">
-        <v>1.026307960097616</v>
+        <v>1.00005048466696</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5280729065227225</v>
+        <v>0.006892503310408223</v>
       </c>
       <c r="P26" t="n">
-        <v>120.7208469149687</v>
+        <v>138.0760469569784</v>
       </c>
       <c r="Q26" t="n">
-        <v>192.6345205821926</v>
+        <v>209.9897206242022</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_6.xlsx
@@ -513,936 +513,936 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_24</t>
+          <t>model_23_6_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998348696980007</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7128654963365189</v>
+        <v>0.6592513803240287</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996655937097193</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.999579169980653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996151192403278</v>
       </c>
       <c r="G2" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.802848052435925e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1704554449393573</v>
+        <v>0.2022831002135905</v>
       </c>
       <c r="I2" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002016698672223108</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004110079352661203</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.0003063389012442155</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.0034634533702214</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009900933315822265</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113232207085</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01032243654483425</v>
       </c>
       <c r="P2" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4605050078386</v>
       </c>
       <c r="Q2" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3741786750625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_23</t>
+          <t>model_23_6_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998348342962443</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7128654963365189</v>
+        <v>0.6592513383285822</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996655150392376</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995790840338283</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996150356196219</v>
       </c>
       <c r="G3" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.804949653625581e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1704554449393573</v>
+        <v>0.2022831251439016</v>
       </c>
       <c r="I3" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.000201717310904008</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004110918761100293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.0003064054576372683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003463631678195246</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009901994573632921</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113256482575</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01032354298258701</v>
       </c>
       <c r="P3" t="n">
-        <v>138.0758540430987</v>
+        <v>136.460076280201</v>
       </c>
       <c r="Q3" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3737499474248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_7</t>
+          <t>model_23_6_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998348061321476</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7128654956957796</v>
+        <v>0.6592512145435827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.999665443543686</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995790211547249</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996149713393693</v>
       </c>
       <c r="G4" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.806621596072147e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1704554453197278</v>
+        <v>0.2022831986280246</v>
       </c>
       <c r="I4" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002017604276120723</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004111532876284095</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.0003064566203454129</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003463795950705989</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009902838782930957</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113275795099</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01032442313162262</v>
       </c>
       <c r="P4" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4597352687788</v>
       </c>
       <c r="Q4" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3734089360026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_8</t>
+          <t>model_23_6_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998347843347238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7128654956957796</v>
+        <v>0.6592511956686977</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996653888817393</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995789720740176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996149202202915</v>
       </c>
       <c r="G5" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.807915585307759e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1704554453197278</v>
+        <v>0.2022832098329716</v>
       </c>
       <c r="I5" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002017933925049606</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004112012228024005</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.0003064973076536806</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003463837535435945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009903492103953918</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113290741904</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01032510426587409</v>
       </c>
       <c r="P5" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4594713850632</v>
       </c>
       <c r="Q5" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3731450522871</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_9</t>
+          <t>model_23_6_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998347046655279</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7128654956957796</v>
+        <v>0.6592509847278489</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996651876496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995787936101096</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996147343918445</v>
       </c>
       <c r="G6" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.812645092929175e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1704554453197278</v>
+        <v>0.2022833350565717</v>
       </c>
       <c r="I6" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002019147492497227</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004113755214002491</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306645214455675</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003464295631922506</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009905879614112607</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000050489536791</v>
+        <v>1.00011334537221</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01032759341728306</v>
       </c>
       <c r="P6" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4585071908609</v>
       </c>
       <c r="Q6" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3721808580848</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_10</t>
+          <t>model_23_6_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998346233049963</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7128654956957796</v>
+        <v>0.6592508495807785</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996649882765744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995786075983012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996145446367448</v>
       </c>
       <c r="G7" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.817475005545436e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1704554453197278</v>
+        <v>0.2022834152857107</v>
       </c>
       <c r="I7" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002020349848217724</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.000411557191732255</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.0003067962466058935</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003464750273651743</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009908317216129808</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113401162288</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033013479306467</v>
       </c>
       <c r="P7" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4575230068234</v>
       </c>
       <c r="Q7" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3711966740473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_22</t>
+          <t>model_23_6_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998346174501451</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592507190468917</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.999664978252867</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995785915436332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996145311881841</v>
       </c>
       <c r="G8" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.817822574800148e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022834927762647</v>
       </c>
       <c r="I8" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002020410298029569</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004115728716876636</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.0003068069507453103</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003464732250114694</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009908492607253712</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113405177043</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033031765095182</v>
       </c>
       <c r="P8" t="n">
-        <v>138.0758540430987</v>
+        <v>136.457452201835</v>
       </c>
       <c r="Q8" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3711258690588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_21</t>
+          <t>model_23_6_8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345900302836</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592506197913093</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996649123882165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995785280410853</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144672748691</v>
       </c>
       <c r="G9" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.819450336227638e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.202283551698666</v>
       </c>
       <c r="I9" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002020807506924922</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116348920995057</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306857821395999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003464877961307092</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009909313970314816</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113423979234</v>
       </c>
       <c r="O9" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033117398113889</v>
       </c>
       <c r="P9" t="n">
-        <v>138.0758540430987</v>
+        <v>136.457120636156</v>
       </c>
       <c r="Q9" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3707943033799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_20</t>
+          <t>model_23_6_7</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.999834594165246</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592506109141261</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996649238585705</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995785366681756</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144769133462</v>
       </c>
       <c r="G10" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.819204866996394e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022835569685454</v>
       </c>
       <c r="I10" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.000202073833284418</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116264663635881</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306850149824003</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003464885463505206</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009909190111707614</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113421143831</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033104484961436</v>
       </c>
       <c r="P10" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4571706333129</v>
       </c>
       <c r="Q10" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3708443005368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_19</t>
+          <t>model_23_6_22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G11" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I11" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P11" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q11" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_18</t>
+          <t>model_23_6_21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G12" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I12" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O12" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P12" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q12" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_17</t>
+          <t>model_23_6_20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G13" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I13" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M13" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P13" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q13" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_16</t>
+          <t>model_23_6_19</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G14" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I14" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O14" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P14" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q14" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_15</t>
+          <t>model_23_6_18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7128654955887277</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G15" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1704554453832784</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I15" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M15" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O15" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P15" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q15" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_12</t>
+          <t>model_23_6_17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7128654955133256</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G16" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1704554454280404</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I16" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M16" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O16" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P16" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q16" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_13</t>
+          <t>model_23_6_16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7128654955133256</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G17" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1704554454280404</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I17" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M17" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P17" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q17" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_11</t>
+          <t>model_23_6_12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7128654955133256</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G18" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1704554454280404</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I18" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M18" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O18" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P18" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q18" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="19">
@@ -1452,437 +1452,437 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7128654955133256</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G19" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1704554454280404</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I19" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M19" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O19" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P19" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q19" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_6</t>
+          <t>model_23_6_13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7128654951043616</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G20" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1704554456708191</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I20" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M20" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O20" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P20" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q20" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_5</t>
+          <t>model_23_6_23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7128654951043616</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G21" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1704554456708191</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I21" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L21" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M21" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O21" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P21" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q21" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_4</t>
+          <t>model_23_6_11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7128654951043616</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G22" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1704554456708191</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I22" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M22" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O22" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P22" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q22" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_3</t>
+          <t>model_23_6_10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999263694255129</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7128654951043616</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9997460653257515</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9995013370301891</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9996639445085993</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G23" t="n">
-        <v>4.371028969071967e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1704554456708191</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I23" t="n">
-        <v>5.955371742230982e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002136355922241635</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0001365944592225912</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001741122342325455</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M23" t="n">
-        <v>0.006611375778967617</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000050489536791</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O23" t="n">
-        <v>0.006892835733312844</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P23" t="n">
-        <v>138.0758540430987</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q23" t="n">
-        <v>209.9895277103226</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_2</t>
+          <t>model_23_6_15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999263754483461</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7128652799263899</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9997460777286551</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9995013824061324</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9996639710376358</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G24" t="n">
-        <v>4.37067142767776e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1704555734097583</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I24" t="n">
-        <v>5.955080864659403e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0002136161524078265</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K24" t="n">
-        <v>0.000136583676124303</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001741202467651817</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M24" t="n">
-        <v>0.006611105374805155</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000050485406848</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O24" t="n">
-        <v>0.006892553817485372</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P24" t="n">
-        <v>138.0760176457747</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q24" t="n">
-        <v>209.9896913129986</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_1</t>
+          <t>model_23_6_24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999263764055933</v>
+        <v>0.9998345658137406</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7128651837675973</v>
+        <v>0.6592505249658671</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9997460816622732</v>
+        <v>0.9996648564112407</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9995013885447002</v>
+        <v>0.9995784706059123</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9996639758887256</v>
+        <v>0.9996144108299739</v>
       </c>
       <c r="G25" t="n">
-        <v>4.370614601345083e-05</v>
+        <v>9.820887934826661e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1704556304937714</v>
+        <v>0.2022836079911448</v>
       </c>
       <c r="I25" t="n">
-        <v>5.954988611963723e-05</v>
+        <v>0.0002021145086378625</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0002136135225423048</v>
+        <v>0.0004116909867475434</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000136581704330971</v>
+        <v>0.000306902747692703</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001741170056908033</v>
+        <v>0.003465019223575216</v>
       </c>
       <c r="M25" t="n">
-        <v>0.006611062396729502</v>
+        <v>0.009910039321227066</v>
       </c>
       <c r="N25" t="n">
-        <v>1.00005048475045</v>
+        <v>1.000113440584864</v>
       </c>
       <c r="O25" t="n">
-        <v>0.006892509009744062</v>
+        <v>0.01033193021174116</v>
       </c>
       <c r="P25" t="n">
-        <v>138.0760436494234</v>
+        <v>136.4568278512596</v>
       </c>
       <c r="Q25" t="n">
-        <v>209.9897173166472</v>
+        <v>208.3705015184835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_0</t>
+          <t>model_23_6_9</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999263765273503</v>
+        <v>0.9998345715692901</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7128651703111351</v>
+        <v>0.6592505225507056</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9997460923727292</v>
+        <v>0.999664865540234</v>
       </c>
       <c r="E26" t="n">
-        <v>0.99950138373826</v>
+        <v>0.9995784868343451</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9996639748200138</v>
+        <v>0.999614424344614</v>
       </c>
       <c r="G26" t="n">
-        <v>4.370607373326924e-05</v>
+        <v>9.820546260550031e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1704556384821087</v>
+        <v>0.202283609424889</v>
       </c>
       <c r="I26" t="n">
-        <v>5.954737426313043e-05</v>
+        <v>0.0002021090032304319</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0002136155817019754</v>
+        <v>0.0004116751370830115</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0001365821387238394</v>
+        <v>0.000306891990958531</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001741192102065642</v>
+        <v>0.003464989287118092</v>
       </c>
       <c r="M26" t="n">
-        <v>0.006611056930118606</v>
+        <v>0.009909866931775639</v>
       </c>
       <c r="N26" t="n">
-        <v>1.00005048466696</v>
+        <v>1.000113436638201</v>
       </c>
       <c r="O26" t="n">
-        <v>0.006892503310408223</v>
+        <v>0.01033175048331389</v>
       </c>
       <c r="P26" t="n">
-        <v>138.0760469569784</v>
+        <v>136.4568974336075</v>
       </c>
       <c r="Q26" t="n">
-        <v>209.9897206242022</v>
+        <v>208.3705711008313</v>
       </c>
     </row>
   </sheetData>
